--- a/config/level_config_v2.xlsx
+++ b/config/level_config_v2.xlsx
@@ -27194,7 +27194,7 @@
       <c r="N279" s="0" t="inlineStr"/>
       <c r="O279" s="0" t="inlineStr">
         <is>
-          <t>防御</t>
+          <t>防卫</t>
         </is>
       </c>
       <c r="P279" s="0" t="inlineStr">
@@ -27204,7 +27204,7 @@
       </c>
       <c r="Q279" s="0" t="inlineStr">
         <is>
-          <t>闭路电视</t>
+          <t>监控</t>
         </is>
       </c>
       <c r="R279" s="0" t="inlineStr">
